--- a/nexidoc/Nexi_Purchasing_Audit_v22.31.xlsx
+++ b/nexidoc/Nexi_Purchasing_Audit_v22.31.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7"/>
@@ -1344,12 +1344,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>SOS code first, exact name second; a substring is a possible match a person confirms and never makes a PR not required (test purch-audit-v2231).</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
           <t>The catalogue hint matches the FIRST item whose name merely contains the PR text; if its on-hand ≥ qty the verdict is 'No purchase — stock covers need' at 95% confidence.</t>
@@ -1382,12 +1386,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Purchasing Review names the buyer (kept with who reviewed); Inventory Verification keeps the SOS snapshot per line (test purch-audit-v2231).</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
           <t>'Purchasing Review' and 'Inventory Verification' are one-click pass-throughs; no buyer assigned, no verification result stored.</t>
@@ -1420,12 +1428,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Completing with goods missing needs Eyal / Dr Amy and a reason and closes the PO short; closed POs raise no delivery alerts (test purch-audit-v2231).</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t>'Complete anyway' closes a PR with nothing received; the PO stays Issued and Mission Control keeps alerting 'PO past delivery date' forever.</t>
@@ -1458,12 +1470,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>DRAFT OPENED until ✓ Sent; the supplier reply rate counts only RFQs really sent or answered.</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
           <t>'SENT' is stamped as soon as a mailto:/sms: link opens; nothing confirms a send. Reply rate divides by these.</t>
@@ -1496,12 +1512,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>On time = last accepted delivery ≤ promised date (issued + lead days), else need-by; one sample per PO (test purch-audit-v2231).</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
           <t>On-time uses the PR need-by date, not the supplier's promised lead time; each GRN counts as a sample.</t>
@@ -1984,12 +2004,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Cancelled / void SOS POs are skipped and their earlier rows removed; received qty is used; lines with nothing received are left out (test purch-audit-v2231).</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Every SOS PO line is imported as a purchase: cancelled/voided POs included, ordered qty used instead of received.</t>
@@ -2330,14 +2354,14 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>acct_vendors links still target an unregistered view.</t>
+          <t>acct_vendors is a hidden Accounting view, so Vendors links keep the Accounting header (test purch-audit-v2231).</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2490,12 +2514,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Rows with source rfq-quote are not counted as purchases (test purch-audit-v2231).</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
           <t>Quote rows (qty 0) sit in the same history store and are counted as purchases.</t>
@@ -2992,14 +3020,14 @@
           <t>critical</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Partly v21.65</t>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Purchase-type requests now flow to Purchasing via 📥 From Inventory; the Inventory-side stock-OUT booking is still there if someone confirms there.</t>
+          <t>"Confirm issued" is refused on a Purchase request — no stock out; it goes to Purchasing (📥 From Inventory), shows Ordered, and stock rises only on receipt (test purch-audit-v2231).</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3118,12 +3146,16 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Partly v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>No self-approval or self-override; a second level by the same person is asked and logged (test purch-audit-v2231). The level → person matrix still needs the owner.</t>
+        </is>
+      </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Every chain level (Dept Manager, Division Head, VP/COO, Procurement, Accounting, HR) is approved by whoever has manageInventory; requester may approve own request.</t>
@@ -3156,12 +3188,16 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Warehouse ▸ Reorder opens a Purchase request, not a Stock Issue (test purch-audit-v2231).</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Warehouse 'reorder' prefills a request without a type, so it defaults to Stock Issue and posts a NEGATIVE adjustment instead of a PO.</t>
@@ -3350,12 +3386,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>The Inventory request is Ordered while Purchasing works it and completes on the GRN that fully receives its PO (test purch-audit-v2231).</t>
+        </is>
+      </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
           <t>Pasting any text as SOS reference marks a purchase 'completed'; nothing links it to a receipt; the request leaves the open queue before goods arrive.</t>
@@ -3582,14 +3622,14 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>Partly v22.31 (trial)</t>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Supplier 360° closes with Escape and a click outside and sits above every banner; the outreach and location modals are still to do.</t>
+          <t>Supplier 360°, the outreach and the delivery-location modals close with Escape or a click outside and sit above every banner (test purch-audit-v2231).</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3708,12 +3748,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Every stage button toasts the new stage.</t>
+        </is>
+      </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
           <t>Approve, Reviewed, Verified and Run AI advance the stage silently (no toast); Submit, Accept and Override do.</t>
@@ -3746,12 +3790,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr"/>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Fixed v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>No issued PO → "Issue a purchase order first" instead of the Log &amp; match button (test purch-audit-v2231).</t>
+        </is>
+      </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
           <t>Invoices tab shows an empty PO select on a fresh install; the only guard is 'PO, invoice number and amount are required.'</t>

--- a/nexidoc/Nexi_Purchasing_Audit_v22.31.xlsx
+++ b/nexidoc/Nexi_Purchasing_Audit_v22.31.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7"/>
@@ -2316,12 +2316,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Partly v22.31 (trial)</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Vendors rows can be edited; adding an existing name offers to update it (test purch-audit-v2231). The other writers still append by name.</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Three writers append vendors with no duplicate check; the Vendors list has no edit.</t>
